--- a/sample_data/sample_output.xlsx
+++ b/sample_data/sample_output.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,85 +413,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ProfitCentre1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>SupplierName</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SupplierGSTIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DocumentDate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>InvoiceValue</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>IGST Amt</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AvailableCGST</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>CRDRPreGST</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>AvailableCGST</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CessRateSpecific</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>SGST Amount</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>HSNorSAC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>DocumentNumber</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>PurchaseVoucherNumber</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ITCReversalIdentifier</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Vendor A</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27AABCU9603R1ZX</t>
+          <t>TechCorp Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>15000</v>
+          <t>29AAKCS3836BIZS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>2700</v>
+        <v>50000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -512,51 +508,69 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>8471</v>
+        <v>9983</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>INV-001</t>
+          <t>INV-2024-001</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>VCH-991</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Vendor B</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29AAKCS3836BIZS</t>
+          <t>Acme Industries</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>42000</v>
+          <t>27AABCU9603R1ZX</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>7560</v>
+        <v>120000</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="I3" t="n">
-        <v>9403</v>
+        <v>8471</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>INV-002</t>
+          <t>INV-2024-002</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>VCH-992</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>

--- a/sample_data/sample_output.xlsx
+++ b/sample_data/sample_output.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ProfitCentre1</t>
+          <t>Unnamed: 3</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -444,14 +444,14 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>IGST Value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>AvailableCGST</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CRDRPreGST</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>SGST Amount</t>
@@ -474,7 +474,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ITCReversalIdentifier</t>
+          <t>ITC Eligible</t>
         </is>
       </c>
     </row>
